--- a/pensum/ok03/OK03_Bedriftens_regnskap_Oppgaver_v6.xlsx
+++ b/pensum/ok03/OK03_Bedriftens_regnskap_Oppgaver_v6.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="280">
   <si>
     <t xml:space="preserve">Bedriftens regnskap: oppgaver til kapittel 3</t>
   </si>
@@ -77,10 +77,19 @@
     <t xml:space="preserve">Dette er øvingsmateriell til repetisjons- og øvingsstøtte. I besvarelser, caser, prosjektoppgaver og eksamen gjelder lærebøkene og oppgitte primærkilder.</t>
   </si>
   <si>
+    <t xml:space="preserve">Det stiger</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1A: Nordlys 2026: sett opp resultatregnskapet</t>
   </si>
   <si>
+    <t xml:space="preserve">Det synker</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alene, i par eller i gruppe, slik du vil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Det endres ikke</t>
   </si>
   <si>
     <t xml:space="preserve">Situasjonen</t>
@@ -217,7 +226,16 @@
     <t xml:space="preserve">Gule celler fyller du inn. Grønne regnes ut av arket. Sjekken til høyre forteller om svaret stemmer, og hva du bør se på hvis ikke.</t>
   </si>
   <si>
+    <t xml:space="preserve">Aktiveres og avskrives</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1B: Fire kjøp i januar: eiendel eller kostnad?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kostnad med én gang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varekostnad</t>
   </si>
   <si>
     <t xml:space="preserve">Tom (driftsleder) har handlet i januar 2027: en servicebil, et varmekamera, en boremaskin og kabel til en jobb. Han spør hvor mye av dette som er kostnad i år, og hvorfor regnskapsføreren sier at bilen nesten ikke koster noe i 2027.</t>
@@ -286,9 +304,15 @@
     <t xml:space="preserve">d) Forskjellen mellom a og b er penger som har gått ut, men ikke er kostnad ennå. Hvor i regnskapet finner du dem igjen, og hva skjer med dem de neste årene? To setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ja, i resultatregnskapet</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1C: Fjell Elektro: resultatregnskapet for første driftsår</t>
   </si>
   <si>
+    <t xml:space="preserve">Nei, i balansen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fjell Elektro AS i Oslo har levert regnskapet for første driftsår, og det ble som budsjettert. Eieren vil vite hva bedriften tjente, og hva som egentlig hører hjemme i resultatregnskapet.</t>
   </si>
   <si>
@@ -305,9 +329,6 @@
   </si>
   <si>
     <t xml:space="preserve">Salgsinntekter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varekostnad</t>
   </si>
   <si>
     <t xml:space="preserve">Lønnskostnad (1 820 000 × 1,468)</t>
@@ -368,12 +389,27 @@
     <t xml:space="preserve">f) Eieren sier: «Vi tjente 83 257 kr første året. Det er godt nok.» Hva ville et driftsregnskap (internregnskap) med kalkulatoriske kostnader vise? Regn med 5 % rente på egenkapitalen på 300 000. To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Anleggsmidler</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 2A: Nordlys' balanse: grupper postene før bankmøtet</t>
   </si>
   <si>
+    <t xml:space="preserve">Omløpsmidler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egenkapital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langsiktig gjeld</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kari skal i banken om kassekreditten, og banken har bedt om balansen per 31.12.2026. Regnskapsføreren har sendt postene i tilfeldig rekkefølge. Grupper dem i anleggsmidler, omløpsmidler, egenkapital, langsiktig gjeld og kortsiktig gjeld, og regn summene banken spør etter.</t>
   </si>
   <si>
+    <t xml:space="preserve">Kortsiktig gjeld</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eiendeler = egenkapital + gjeld. Anleggsmidler skal brukes i flere år; omløpsmidler er på vei til å bli penger i løpet av året. Egenkapital er aksjekapital pluss opptjent overskudd. Langsiktig gjeld forfaller om mer enn ett år, kortsiktig gjeld innen ett år.</t>
   </si>
   <si>
@@ -443,7 +479,16 @@
     <t xml:space="preserve">e) Banken spør: tåler Nordlys et dårlig år? Bruk lærebokas to tommelfingerregler: egenkapital pluss langsiktig gjeld mot anleggsmidlene, og kortsiktig gjeld mot omløpsmidlene. To–tre setninger med tall.</t>
   </si>
   <si>
+    <t xml:space="preserve">I resultatregnskapet, som kostnad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 2B: Fjell Elektro: fra åpningsbalanse til balansen etter første år</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I balansen: bankinnskudd ned og banklån ned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Begge steder</t>
   </si>
   <si>
     <t xml:space="preserve">Fjell Elektro AS startet 1. januar med 300 000 kr i aksjekapital og 500 000 kr i banklån. Første driftsår ga 83 257 kr i årsresultat (oppgave 1C). Eieren vil vite hva balansen viser 31. desember, og om han kan ta ut utbytte.</t>
@@ -525,22 +570,52 @@
     <t xml:space="preserve">f) Eieren sier: «Vi har 383 257 i egenkapital. Da tar jeg ut 80 000 i utbytte.» Hva sier du? Bruk bankinnskuddet 563 257, den kortsiktige gjelden 600 000 og kravet i aksjeloven om forsvarlig egenkapital og likviditet. To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Glemt eller telt to ganger</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 2C: Tre balanser som ikke går opp, og svaret til Tom</t>
   </si>
   <si>
+    <t xml:space="preserve">Står på feil side</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egenkapitalen er ikke oppdatert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anleggsmidlene er ikke satt ned</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tre studenter har satt opp Nordlys' balanse per 31.12.2026, og ingen av dem går opp. Samtidig sier Tom (driftsleder): «Vi har 2,9 millioner i egenkapital. Vi har råd til lastebilen.» Finn feilene, og forklar Tom hva egenkapitalen er.</t>
   </si>
   <si>
+    <t xml:space="preserve">Regnefeil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kassekreditten</t>
+  </si>
+  <si>
     <t xml:space="preserve">Balansen balanserer fordi egenkapitalen er definert som eiendeler minus gjeld, og fordi hver hendelse treffer to poster med samme beløp (dobbelt bokholderi). En balanse som ikke går opp, er alltid en feil i oppsettet. Differansen mellom sidene forteller som regel hvilken.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bankinnskuddet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anleggsmidlene</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nordlys' riktige balanse per 31.12.2026 (kroner)</t>
   </si>
   <si>
     <t xml:space="preserve">Eiendeler: verktøy, instrumenter og biler 3 600 000, varelager 1 400 000, kundefordringer 4 200 000, bankinnskudd 982 650, sum 10 182 650. Egenkapital og gjeld: aksjekapital 300 000, annen egenkapital 2 592 650, banklån 2 800 000, leverandørgjeld 2 100 000, skyldige avgifter 1 200 000, skyldige feriepenger 890 000, kassekreditt 300 000, sum 10 182 650. Fra resultatregnskapet 2026: avskrivninger 620 000, årsresultat 910 650.</t>
   </si>
   <si>
+    <t xml:space="preserve">Kundefordringene</t>
+  </si>
+  <si>
     <t xml:space="preserve">De fem feilene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avskrivningene</t>
   </si>
   <si>
     <t xml:space="preserve">Regn differansen mellom sidene først. Er den lik én post, er posten glemt eller telt to ganger. Er den det dobbelte av en post, står posten på feil side. Er den lik årsresultatet, er egenkapitalen ikke oppdatert. Er den lik avskrivningen, er anleggsmidlene ikke satt ned. Likner den ikke på noe, er det regnefeil.</t>
@@ -988,7 +1063,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1011,6 +1086,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1472,7 +1551,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G58"/>
+  <dimension ref="B1:Z58"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1480,453 +1559,465 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>25</v>
+      <c r="B11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>10660000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>22400000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>232500</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>7990000</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>620000</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>1386000</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>256850</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="12" t="n">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>22400000</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="14"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="14"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>10660000</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>620000</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>1386000</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="14"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="13" t="n">
         <v>232500</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>7990000</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>620000</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>56000</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="12" t="n">
-        <v>1386000</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="12" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="14"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="13" t="n">
         <v>256850</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="12" t="n">
-        <v>22400000</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="13"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="13"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="12" t="n">
-        <v>10660000</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="12" t="n">
-        <v>620000</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="12" t="n">
-        <v>1386000</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="13"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="12" t="n">
-        <v>56000</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="12" t="n">
-        <v>232500</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="13"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C35" s="12" t="n">
-        <v>256850</v>
-      </c>
-    </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="13"/>
+      <c r="B36" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="14"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
+      <c r="B38" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
     </row>
     <row r="39" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
+      <c r="B39" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="14" t="s">
-        <v>51</v>
+      <c r="B41" s="15" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="C42" s="15" t="str">
+        <v>55</v>
+      </c>
+      <c r="C42" s="16" t="str">
         <f aca="false">IF(C26="","Skriv svaret i cellen C26.",IF(C26=(7990000+400000),"Riktig.",IF(C26=(7990000),"Du har tatt bare materiellet. De innleide montørene, 400 000, er også varekostnad hos Nordlys.","Ikke riktig ennå. Varekostnaden er materiell 7 990 000 pluss innleide montører 400 000.")))</f>
         <v>Skriv svaret i cellen C26.</v>
       </c>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
     </row>
     <row r="43" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C43" s="15" t="str">
+        <v>56</v>
+      </c>
+      <c r="C43" s="16" t="str">
         <f aca="false">IF(C27="","Skriv svaret i cellen C27.",IF(C27=(C25-(C26)),"Riktig.",IF(C27=(C25-7990000),"Du har trukket fra bare materiellet. Begge varekostnadene skal fra, til sammen 8 390 000.",IF(C27=(C25-(C26)-C28),"Du har trukket fra lønna også. Bruttofortjenesten er salg minus varekostnad, før lønn.","Ikke riktig ennå. Bruttofortjeneste er salgsinntekt minus varekostnaden samlet."))))</f>
         <v>Skriv svaret i cellen C27.</v>
       </c>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
     </row>
     <row r="44" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C44" s="15" t="str">
+        <v>57</v>
+      </c>
+      <c r="C44" s="16" t="str">
         <f aca="false">IF(C31="","Skriv svaret i cellen C31.",IF(C31=(C25-(C26)-C28-C29-C30),"Riktig.",IF(C31=(C25-(C26)-C28-C30),"Du har glemt avskrivningene, 620 000. De er en driftskostnad.",IF(C31=(C25-(C26)-C28-C29-C30+C32-C33),"Du har tatt med rentene. De står under driftsresultatet; driftsresultatet er før renter.",IF(C31=(C25-C28-C29-C30),"Du har glemt varekostnaden. Driftsresultatet er etter alle driftskostnadene.","Ikke riktig ennå. Driftsresultat er bruttofortjenesten minus lønn, avskrivninger og andre driftskostnader.")))))</f>
         <v>Skriv svaret i cellen C31.</v>
       </c>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
     </row>
     <row r="45" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" s="15" t="str">
+        <v>58</v>
+      </c>
+      <c r="C45" s="16" t="str">
         <f aca="false">IF(C34="","Skriv svaret i cellen C34.",IF(C34=(C25-(C26)-C28-C29-C30+C32-C33),"Riktig.",IF(C34=(C25-(C26)-C28-C29-C30-C33),"Du har glemt renteinntektene, 56 000. De legges til.",IF(C34=(C25-(C26)-C28-C29-C30-C32-C33),"Du har trukket fra renteinntektene. De er en inntekt og legges til; bare rentekostnadene trekkes fra.","Ikke riktig ennå. Resultat før skatt er driftsresultat pluss renteinntekter minus rentekostnader."))))</f>
         <v>Skriv svaret i cellen C34.</v>
       </c>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
     </row>
     <row r="46" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C46" s="15" t="str">
+        <v>59</v>
+      </c>
+      <c r="C46" s="16" t="str">
         <f aca="false">IF(C36="","Skriv svaret i cellen C36.",IF(C36=(C25-(C26)-C28-C29-C30+C32-C33-C35),"Riktig.",IF(C36=(C25-(C26)-C28-C29-C30+C32-C33),"Det er resultat før skatt. Skattekostnaden på 256 850 skal trekkes fra.","Ikke riktig ennå. Årsresultat er resultat før skatt minus skattekostnaden.")))</f>
         <v>Skriv svaret i cellen C36.</v>
       </c>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" s="17"/>
-      <c r="G48" s="18" t="str">
+      <c r="B48" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" s="18"/>
+      <c r="G48" s="19" t="str">
         <f aca="false">IF(C48="","Velg i nedtrekksmenyen.",IF(C48="Det endres ikke","Riktig. Avdrag er ikke en kostnad, og rentene står under driftsresultatet. Driftsresultatet viser driften, ikke finansieringen. Rentekostnadene blir lavere, så resultat før skatt stiger, men driftsresultatet er det samme.","Ikke riktig. Avdrag er ikke en kostnad, og rentene står under driftsresultatet. Driftsresultatet viser driften, ikke finansieringen. Rentekostnadene blir lavere, så resultat før skatt stiger, men driftsresultatet er det samme."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
+      <c r="B50" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
     </row>
     <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
     </row>
     <row r="54" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="20" t="str">
+      <c r="B54" s="21" t="str">
         <f aca="false">IF(LEN(B51)&lt;40,"",IF(AND(ISNUMBER(SEARCH("drift",B51)),ISNUMBER(SEARCH("rente",B51))),"Bra: du peker på driftsresultatet og forklarer at rentene handler om finansieringen, ikke om driften.",IF(OR(ISNUMBER(SEARCH("drift",B51)),ISNUMBER(SEARCH("rente",B51))),"Du er på sporet. Si også hvorfor rentene står under driftsresultatet: de avhenger av hvor mye Nordlys har lånt, ikke av hvor godt jobben gjøres.","Tips: driftsresultatet, 1 344 000, er det ærligste svaret på om driften bærer seg. Rentene står under fordi de handler om hvordan bedriften er finansiert, ikke om hvor godt den drives.")))</f>
         <v/>
       </c>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C55" s="17"/>
+      <c r="B55" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="18"/>
     </row>
     <row r="56" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="21" t="str">
+      <c r="B56" s="22" t="str">
         <f aca="false">IF(C55="JA","Hint: Varekostnad 7 990 000 + 400 000 = 8 390 000. Bruttofortjeneste 22 400 000 − 8 390 000 = 14 010 000. Driftsresultat 14 010 000 − 10 660 000 − 620 000 − 1 386 000 = 1 344 000. Resultat før skatt 1 344 000 + 56 000 − 232 500 = 1 167 500. Årsresultat 1 167 500 − 256 850 = 910 650.","")</f>
         <v/>
       </c>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
-      <c r="G56" s="21"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
     </row>
     <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
+      <c r="B58" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -2003,7 +2094,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C48" type="list">
-      <formula1>"Det stiger,Det synker,Det endres ikke"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C55" type="list">
@@ -2026,7 +2117,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G38"/>
+  <dimension ref="B1:Z38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2034,323 +2125,364 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>64</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z11" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="10" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>450000</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z12" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>5</v>
-      </c>
-    </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>42000</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="13" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="12" t="n">
+      <c r="B14" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>3500</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="13" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="B15" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="13" t="n">
         <v>38000</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+      <c r="B17" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="B18" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
+      <c r="B20" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="17"/>
-      <c r="G21" s="18" t="str">
+      <c r="B21" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="18"/>
+      <c r="G21" s="19" t="str">
         <f aca="false">IF(C21="","Velg i nedtrekksmenyen.",IF(C21="Aktiveres og avskrives","Riktig. Over 30 000 kr og minst tre års brukstid: eiendel i balansen, 450 000 / 5 = 90 000 kr i avskrivning hvert år.","Ikke riktig. Over 30 000 kr og minst tre års brukstid: eiendel i balansen, 450 000 / 5 = 90 000 kr i avskrivning hvert år."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="17"/>
-      <c r="G22" s="18" t="str">
+      <c r="B22" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="G22" s="19" t="str">
         <f aca="false">IF(C22="","Velg i nedtrekksmenyen.",IF(C22="Aktiveres og avskrives","Riktig. Over 30 000 kr og minst tre års brukstid, selv om det er et lite instrument. 42 000 / 6 = 7 000 kr i året.","Ikke riktig. Over 30 000 kr og minst tre års brukstid, selv om det er et lite instrument. 42 000 / 6 = 7 000 kr i året."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="17"/>
-      <c r="G23" s="18" t="str">
+      <c r="B23" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="G23" s="19" t="str">
         <f aca="false">IF(C23="","Velg i nedtrekksmenyen.",IF(C23="Kostnad med én gang","Riktig. Under 30 000 kr: hele beløpet er kostnad i kjøpsåret, selv om den varer i tre år.","Ikke riktig. Under 30 000 kr: hele beløpet er kostnad i kjøpsåret, selv om den varer i tre år."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="G24" s="18" t="str">
+      <c r="B24" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="G24" s="19" t="str">
         <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="Varekostnad","Riktig. Over 30 000 kr, men det er ikke et driftsmiddel. Det er brukt opp hos kunden og er varekostnad.","Ikke riktig. Over 30 000 kr, men det er ikke et driftsmiddel. Det er brukt opp hos kunden og er varekostnad."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G26" s="18" t="str">
+      <c r="B26" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26" s="19" t="str">
         <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(C26=(450000/5+42000/6+3500+38000),"Riktig.",IF(ABS(C26-(450000+42000+3500+38000))&lt;=0,"Du har tatt hele beløpene. Bilen og kameraet aktiveres; bare avskrivningen er kostnad i år.",IF(ABS(C26-(450000/5+42000/6))&lt;=0,"Du har tatt bare avskrivningene. Boremaskinen og kabelen er kostnad i år, med hele beløpet.",IF(ABS(C26-(450000/5+42000/6+3500))&lt;=0,"Du har glemt kabelen, 38 000. Den er varekostnad i år.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27" s="18" t="str">
+      <c r="B27" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="19" t="str">
         <f aca="false">IF(C27="","Skriv svaret i den gule cellen.",IF(C27=(450000+42000+3500+38000),"Riktig.",IF(ABS(C27-(450000/5+42000/6+3500+38000))&lt;=0,"Det er kostnaden i år. Pengene gikk ut med hele beløpet da det ble kjøpt; avskrivning er ikke en utbetaling.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" s="18" t="str">
+      <c r="B28" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="14"/>
+      <c r="D28" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G28" s="19" t="str">
         <f aca="false">IF(C28="","Skriv svaret i den gule cellen.",IF(C28=(450000-2*450000/5),"Riktig.",IF(ABS(C28-(450000-450000/5))&lt;=0,"Du har trukket fra ett års avskrivning. Ved utgangen av 2028 er det gått to år: 2 × 90 000.",IF(ABS(C28-(2*450000/5))&lt;=0,"Det er summen av de to avskrivningene, 180 000. Bokført verdi er det som er igjen: 450 000 minus 180 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="B30" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="20" t="str">
+      <c r="B34" s="21" t="str">
         <f aca="false">IF(LEN(B31)&lt;40,"",IF(AND(ISNUMBER(SEARCH("balanse",B31)),ISNUMBER(SEARCH("avskriv",B31))),"Bra: du sier at forskjellen står i balansen som eiendel, og at den blir kostnad gjennom avskrivningene de neste årene.",IF(OR(ISNUMBER(SEARCH("balanse",B31)),ISNUMBER(SEARCH("avskriv",B31))),"Du er på sporet. Si både hvor pengene står nå (i balansen, som bil og kamera) og hva som skjer med dem videre (avskrivningene).","Tips: 533 500 − 138 500 = 395 000 kr står i balansen som servicebil og varmekamera. De blir kostnad litt hvert år gjennom avskrivningene, 97 000 kr i året.")))</f>
         <v/>
       </c>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35" s="17"/>
+      <c r="B35" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="18"/>
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="21" t="str">
+      <c r="B36" s="22" t="str">
         <f aca="false">IF(C35="JA","Hint: Kostnad i år: 450 000 / 5 = 90 000, pluss 42 000 / 6 = 7 000, pluss 3 500, pluss 38 000 = 138 500. Ut av banken: 450 000 + 42 000 + 3 500 + 38 000 = 533 500. Bilen etter to år: 450 000 − 2 × 90 000 = 270 000.","")</f>
         <v/>
       </c>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
+      <c r="B38" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2429,19 +2561,19 @@
   </conditionalFormatting>
   <dataValidations count="5">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C21" type="list">
-      <formula1>"Aktiveres og avskrives,Kostnad med én gang,Varekostnad"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C22" type="list">
-      <formula1>"Aktiveres og avskrives,Kostnad med én gang,Varekostnad"</formula1>
+      <formula1>$Z$4:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C23" type="list">
-      <formula1>"Aktiveres og avskrives,Kostnad med én gang,Varekostnad"</formula1>
+      <formula1>$Z$7:$Z$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C24" type="list">
-      <formula1>"Aktiveres og avskrives,Kostnad med én gang,Varekostnad"</formula1>
+      <formula1>$Z$10:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C35" type="list">
@@ -2464,7 +2596,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G45"/>
+  <dimension ref="B1:Z45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2472,373 +2604,414 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>89</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>4795000</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>2671760</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>519000</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+    </row>
+    <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+    </row>
+    <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>4795000</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>1400000</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>2671760</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>519000</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="12" t="n">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-    </row>
-    <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="18" t="str">
+      <c r="G24" s="19" t="str">
         <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(C24=(4795000-1400000),"Riktig.",IF(ABS(C24-(4795000-1400000-2671760))&lt;=0,"Du har trukket fra lønna. Bruttofortjenesten er salg minus varekostnad, før lønn.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G25" s="18" t="str">
+      <c r="B25" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" s="19" t="str">
         <f aca="false">IF(C25="","Skriv svaret i den gule cellen.",IF(C25=(4795000-1400000-2671760-300000/5-519000),"Riktig.",IF(ABS(C25-(4795000-1400000-2671760-300000-519000))&lt;=0,"Du har ført hele utstyret på 300 000 som kostnad. Det aktiveres; bare avskrivningen, 60 000, er kostnad i år.",IF(ABS(C25-(4795000-1400000-2671760-519000))&lt;=0,"Du har glemt avskrivningen på utstyret, 300 000 / 5 = 60 000.",IF(ABS(C25-(4795000-1400000-1820000-300000/5-519000))&lt;=0,"Du har brukt lønna uten sosiale kostnader. Lønnskostnaden er 1 820 000 × 1,468 = 2 671 760.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G26" s="18" t="str">
+      <c r="B26" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26" s="19" t="str">
         <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(C26=(4795000-1400000-2671760-300000/5-519000-500000*0.075),"Riktig.",IF(ABS(C26-(4795000-1400000-2671760-300000/5-519000-500000*0.075-100000))&lt;=0,"Du har trukket fra avdraget på 100 000. Avdrag er ikke en kostnad; bare rentene står i resultatregnskapet.",IF(ABS(C26-(4795000-1400000-2671760-300000/5-519000))&lt;=0,"Du har glemt rentene: 500 000 × 7,5 % = 37 500.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27" s="18" t="str">
+      <c r="B27" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="19" t="str">
         <f aca="false">IF(C27="","Skriv svaret i den gule cellen.",IF(ABS(C27-(106740-ROUND(106740*0.22,0)))&lt;=1,"Riktig.",IF(ABS(C27-(106740))&lt;=1,"Det er resultat før skatt. Trekk fra 22 % skatt.",IF(ABS(C27-(ROUND(106740*0.22,0)))&lt;=1,"Det er skatten, 23 483. Årsresultatet er det som er igjen etter skatten.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
+      <c r="B29" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" s="17"/>
-      <c r="G30" s="18" t="str">
+      <c r="B30" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="G30" s="19" t="str">
         <f aca="false">IF(C30="","Velg i nedtrekksmenyen.",IF(C30="Nei, i balansen","Riktig. Utstyret aktiveres og står i balansen som eiendel. Bare avskrivningen er kostnad i år.","Ikke riktig. Utstyret aktiveres og står i balansen som eiendel. Bare avskrivningen er kostnad i år."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C31" s="17"/>
-      <c r="G31" s="18" t="str">
+      <c r="B31" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="G31" s="19" t="str">
         <f aca="false">IF(C31="","Velg i nedtrekksmenyen.",IF(C31="Ja, i resultatregnskapet","Riktig. Driftskostnad: årets del av utstyret.","Ikke riktig. Driftskostnad: årets del av utstyret."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C32" s="17"/>
-      <c r="G32" s="18" t="str">
+      <c r="B32" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="G32" s="19" t="str">
         <f aca="false">IF(C32="","Velg i nedtrekksmenyen.",IF(C32="Nei, i balansen","Riktig. Nedbetaling av gjeld. Banklånet i balansen går ned; resultatet merker ingenting.","Ikke riktig. Nedbetaling av gjeld. Banklånet i balansen går ned; resultatet merker ingenting."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C33" s="17"/>
-      <c r="G33" s="18" t="str">
+      <c r="B33" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="G33" s="19" t="str">
         <f aca="false">IF(C33="","Velg i nedtrekksmenyen.",IF(C33="Ja, i resultatregnskapet","Riktig. Finanskostnad, under driftsresultatet.","Ikke riktig. Finanskostnad, under driftsresultatet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="C34" s="17"/>
-      <c r="G34" s="18" t="str">
+      <c r="B34" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="G34" s="19" t="str">
         <f aca="false">IF(C34="","Velg i nedtrekksmenyen.",IF(C34="Nei, i balansen","Riktig. Eierens innskudd. Egenkapital i balansen, ikke inntekt.","Ikke riktig. Eierens innskudd. Egenkapital i balansen, ikke inntekt."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C35" s="17"/>
-      <c r="G35" s="18" t="str">
+      <c r="B35" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="G35" s="19" t="str">
         <f aca="false">IF(C35="","Velg i nedtrekksmenyen.",IF(C35="Ja, i resultatregnskapet","Riktig. Står mellom resultat før skatt og årsresultatet.","Ikke riktig. Står mellom resultat før skatt og årsresultatet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
+      <c r="B37" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="20" t="str">
+      <c r="B41" s="21" t="str">
         <f aca="false">IF(LEN(B38)&lt;40,"",IF(AND(ISNUMBER(SEARCH("rente",B38)),ISNUMBER(SEARCH("egenkapital",B38))),"Bra: du tar med kalkulatorisk rente på egenkapitalen. 300 000 × 5 % = 15 000 kr er prisen for eierens egne penger, og den står ikke i finansregnskapet.",IF(OR(ISNUMBER(SEARCH("rente",B38)),ISNUMBER(SEARCH("egenkapital",B38))),"Du er på sporet. Regn ut den kalkulatoriske renten på egenkapitalen: 300 000 × 5 % = 15 000 kr, og si hva den gjør med resultatet.","Tips: egenkapitalen har også en pris. 300 000 × 5 % = 15 000 kr i kalkulatorisk rente. Resultat før skatt på 106 740 blir 91 740 i driftsregnskapet. Eierlønnen på 700 000 er allerede kostnad, fordi Fjell er et aksjeselskap.")))</f>
         <v/>
       </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C42" s="17"/>
+      <c r="B42" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="18"/>
     </row>
     <row r="43" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="21" t="str">
+      <c r="B43" s="22" t="str">
         <f aca="false">IF(C42="JA","Hint: a: 4 795 000 − 1 400 000 = 3 395 000. b: 3 395 000 − 2 671 760 − 60 000 − 519 000 = 144 240. c: 144 240 − 37 500 = 106 740. d: skatt 106 740 × 0,22 = 23 483; 106 740 − 23 483 = 83 257. Avdraget og aksjekapitalen står ikke i resultatregnskapet.","")</f>
         <v/>
       </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
+      <c r="B45" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2941,27 +3114,27 @@
   </conditionalFormatting>
   <dataValidations count="7">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
-      <formula1>"Ja,i resultatregnskapet,Nei,i balansen"</formula1>
+      <formula1>$Z$1:$Z$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C31" type="list">
-      <formula1>"Ja,i resultatregnskapet,Nei,i balansen"</formula1>
+      <formula1>$Z$3:$Z$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Ja,i resultatregnskapet,Nei,i balansen"</formula1>
+      <formula1>$Z$5:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C33" type="list">
-      <formula1>"Ja,i resultatregnskapet,Nei,i balansen"</formula1>
+      <formula1>$Z$7:$Z$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C34" type="list">
-      <formula1>"Ja,i resultatregnskapet,Nei,i balansen"</formula1>
+      <formula1>$Z$9:$Z$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C35" type="list">
-      <formula1>"Ja,i resultatregnskapet,Nei,i balansen"</formula1>
+      <formula1>$Z$11:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C42" type="list">
@@ -2984,7 +3157,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G40"/>
+  <dimension ref="B1:Z55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2992,351 +3165,559 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>116</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z11" s="0" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="B12" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="Z12" s="6" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C13" s="17"/>
-      <c r="G13" s="18" t="str">
+      <c r="B13" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="G13" s="19" t="str">
         <f aca="false">IF(C13="","Velg i nedtrekksmenyen.",IF(C13="Omløpsmidler","Riktig. Penger kundene skylder Nordlys. Blir til bankinnskudd når de betaler.","Ikke riktig. Penger kundene skylder Nordlys. Blir til bankinnskudd når de betaler."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z13" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="17"/>
-      <c r="G14" s="18" t="str">
+      <c r="B14" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="G14" s="19" t="str">
         <f aca="false">IF(C14="","Velg i nedtrekksmenyen.",IF(C14="Langsiktig gjeld","Riktig. Gjeld med forfall senere enn ett år fram i tid, med sikkerhet i bilene og utstyret.","Ikke riktig. Gjeld med forfall senere enn ett år fram i tid, med sikkerhet i bilene og utstyret."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z14" s="6" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" s="17"/>
-      <c r="G15" s="18" t="str">
+      <c r="B15" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="G15" s="19" t="str">
         <f aca="false">IF(C15="","Velg i nedtrekksmenyen.",IF(C15="Omløpsmidler","Riktig. Penger på konto er det mest kortsiktige av alt Nordlys eier.","Ikke riktig. Penger på konto er det mest kortsiktige av alt Nordlys eier."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z15" s="6" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="17"/>
-      <c r="G16" s="18" t="str">
+      <c r="B16" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="G16" s="19" t="str">
         <f aca="false">IF(C16="","Velg i nedtrekksmenyen.",IF(C16="Kortsiktig gjeld","Riktig. Opptjent i 2026, betales ut til de ansatte sommeren 2027: innen ett år.","Ikke riktig. Opptjent i 2026, betales ut til de ansatte sommeren 2027: innen ett år."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z16" s="6" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="17"/>
-      <c r="G17" s="18" t="str">
+      <c r="B17" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="18"/>
+      <c r="G17" s="19" t="str">
         <f aca="false">IF(C17="","Velg i nedtrekksmenyen.",IF(C17="Anleggsmidler","Riktig. Skal brukes i flere år, og avskrives.","Ikke riktig. Skal brukes i flere år, og avskrives."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z17" s="6" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18" s="17"/>
-      <c r="G18" s="18" t="str">
+      <c r="B18" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="18"/>
+      <c r="G18" s="19" t="str">
         <f aca="false">IF(C18="","Velg i nedtrekksmenyen.",IF(C18="Egenkapital","Riktig. Det Kari og Tom skjøt inn i 2019.","Ikke riktig. Det Kari og Tom skjøt inn i 2019."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z18" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" s="17"/>
-      <c r="G19" s="18" t="str">
+      <c r="B19" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="G19" s="19" t="str">
         <f aca="false">IF(C19="","Velg i nedtrekksmenyen.",IF(C19="Kortsiktig gjeld","Riktig. Lånte penger fra banken, ikke bankinnskudd. Den vanligste feilen i hele kapitlet.","Ikke riktig. Lånte penger fra banken, ikke bankinnskudd. Den vanligste feilen i hele kapitlet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z19" s="6" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="C20" s="17"/>
-      <c r="G20" s="18" t="str">
+      <c r="B20" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="18"/>
+      <c r="G20" s="19" t="str">
         <f aca="false">IF(C20="","Velg i nedtrekksmenyen.",IF(C20="Omløpsmidler","Riktig. Materiell som skal monteres og faktureres i løpet av året.","Ikke riktig. Materiell som skal monteres og faktureres i løpet av året."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z20" s="6" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="C21" s="17"/>
-      <c r="G21" s="18" t="str">
+      <c r="B21" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="18"/>
+      <c r="G21" s="19" t="str">
         <f aca="false">IF(C21="","Velg i nedtrekksmenyen.",IF(C21="Kortsiktig gjeld","Riktig. Ubetalte fakturaer til Polarlys, forfaller om 30 dager.","Ikke riktig. Ubetalte fakturaer til Polarlys, forfaller om 30 dager."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z21" s="6" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C22" s="17"/>
-      <c r="G22" s="18" t="str">
+      <c r="B22" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="G22" s="19" t="str">
         <f aca="false">IF(C22="","Velg i nedtrekksmenyen.",IF(C22="Egenkapital","Riktig. Overskudd fra tidligere år som er blitt stående i bedriften.","Ikke riktig. Overskudd fra tidligere år som er blitt stående i bedriften."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z22" s="6" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" s="17"/>
-      <c r="G23" s="18" t="str">
+      <c r="B23" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="G23" s="19" t="str">
         <f aca="false">IF(C23="","Velg i nedtrekksmenyen.",IF(C23="Kortsiktig gjeld","Riktig. Skyldes staten og forfaller innen få måneder.","Ikke riktig. Skyldes staten og forfaller innen få måneder."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z23" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z24" s="0" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
+      <c r="B25" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="Z25" s="6" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="B26" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="Z26" s="6" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27" s="18" t="str">
+      <c r="B27" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="19" t="str">
         <f aca="false">IF(C27="","Skriv svaret i den gule cellen.",IF(C27=(1400000+4200000+982650),"Riktig.",IF(ABS(C27-(1400000+4200000+982650+300000))&lt;=0,"Du har tatt med kassekreditten. Den er lånte penger: kortsiktig gjeld, ikke bankinnskudd.",IF(ABS(C27-(4200000+982650))&lt;=0,"Du har glemt varelageret, 1 400 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z27" s="6" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" s="18" t="str">
+      <c r="B28" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="14"/>
+      <c r="D28" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G28" s="19" t="str">
         <f aca="false">IF(C28="","Skriv svaret i den gule cellen.",IF(C28=(2100000+1200000+890000+300000),"Riktig.",IF(ABS(C28-(2100000+1200000+890000))&lt;=0,"Du har glemt kassekreditten, 300 000. Den forfaller innen ett år.",IF(ABS(C28-(2100000+1200000+890000+300000+2800000))&lt;=0,"Du har tatt med banklånet. Det forfaller om over ett år og er langsiktig gjeld.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z28" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29" s="18" t="str">
+      <c r="B29" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" s="14"/>
+      <c r="D29" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" s="19" t="str">
         <f aca="false">IF(C29="","Skriv svaret i den gule cellen.",IF(C29=(3600000+1400000+4200000+982650),"Riktig.",IF(ABS(C29-(3600000+1400000+4200000+982650+300000))&lt;=0,"600 000 for mye, det dobbelte av kassekreditten. Den er lagt til eiendelene i stedet for til gjelden.",IF(ABS(C29-(1400000+4200000+982650))&lt;=0,"Du har glemt anleggsmidlene, 3 600 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z29" s="6" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="C30" s="23"/>
-      <c r="D30" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="G30" s="18" t="str">
+      <c r="B30" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" s="24"/>
+      <c r="D30" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="G30" s="19" t="str">
         <f aca="false">IF(C30="","Skriv svaret i den gule cellen.",IF(ABS(C30-(ROUND((300000+2592650)/(3600000+1400000+4200000+982650)*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C30-(ROUND(300000/(3600000+1400000+4200000+982650)*100,1)))&lt;=0.06,"Du har tatt bare aksjekapitalen. Egenkapitalen er aksjekapital pluss annen egenkapital, 2 892 650.",IF(ABS(C30-(ROUND((300000+2592650)/(2800000+2100000+1200000+890000+300000)*100,1)))&lt;=0.06,"Du har delt på gjelden. Her skal egenkapitalen deles på eiendelene, 10 182 650.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z30" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z31" s="0" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
+      <c r="B32" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="Z32" s="6" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="Z33" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="Z34" s="6" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="Z35" s="6" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="20" t="str">
+      <c r="B36" s="21" t="str">
         <f aca="false">IF(LEN(B33)&lt;40,"",IF(AND(ISNUMBER(SEARCH("anleggsmidl",B33)),ISNUMBER(SEARCH("omløpsmidl",B33))),"Bra: du bruker begge reglene. Egenkapital og langsiktig gjeld, 5 692 650, dekker anleggsmidlene på 3 600 000 med god margin, og omløpsmidlene på 6 582 650 er større enn den kortsiktige gjelden på 4 490 000.",IF(OR(ISNUMBER(SEARCH("anleggsmidl",B33)),ISNUMBER(SEARCH("omløpsmidl",B33))),"Du har den ene regelen. Ta med den andre også: egenkapital pluss langsiktig gjeld mot anleggsmidlene, og kortsiktig gjeld mot omløpsmidlene.","Tips: 2 892 650 + 2 800 000 = 5 692 650 er mer enn anleggsmidlene på 3 600 000. Omløpsmidlene på 6 582 650 er mer enn den kortsiktige gjelden på 4 490 000. Begge reglene er oppfylt, men bare 982 650 av omløpsmidlene er penger på konto.")))</f>
         <v/>
       </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="Z36" s="6" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="17"/>
+      <c r="B37" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="Z37" s="6" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="21" t="str">
+      <c r="B38" s="22" t="str">
         <f aca="false">IF(C37="JA","Hint: Omløpsmidler: 1 400 000 + 4 200 000 + 982 650 = 6 582 650. Kortsiktig gjeld: 2 100 000 + 1 200 000 + 890 000 + 300 000 = 4 490 000. Eiendeler: 3 600 000 + 6 582 650 = 10 182 650. Egenkapital 2 892 650 / 10 182 650 = 28,4 %.","")</f>
         <v/>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="Z38" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z39" s="0" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
+      <c r="B40" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="Z40" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z41" s="0" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z42" s="0" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z43" s="0" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z44" s="0" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z45" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z46" s="0" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z47" s="0" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z48" s="0" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z49" s="0" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z50" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z51" s="0" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z52" s="0" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z53" s="0" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z54" s="0" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z55" s="0" t="s">
+        <v>122</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3479,47 +3860,47 @@
   </conditionalFormatting>
   <dataValidations count="12">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C13" type="list">
-      <formula1>"Anleggsmidler,Omløpsmidler,Egenkapital,Langsiktig gjeld,Kortsiktig gjeld"</formula1>
+      <formula1>$Z$1:$Z$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C14" type="list">
-      <formula1>"Anleggsmidler,Omløpsmidler,Egenkapital,Langsiktig gjeld,Kortsiktig gjeld"</formula1>
+      <formula1>$Z$6:$Z$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C15" type="list">
-      <formula1>"Anleggsmidler,Omløpsmidler,Egenkapital,Langsiktig gjeld,Kortsiktig gjeld"</formula1>
+      <formula1>$Z$11:$Z$15</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C16" type="list">
-      <formula1>"Anleggsmidler,Omløpsmidler,Egenkapital,Langsiktig gjeld,Kortsiktig gjeld"</formula1>
+      <formula1>$Z$16:$Z$20</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C17" type="list">
-      <formula1>"Anleggsmidler,Omløpsmidler,Egenkapital,Langsiktig gjeld,Kortsiktig gjeld"</formula1>
+      <formula1>$Z$21:$Z$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C18" type="list">
-      <formula1>"Anleggsmidler,Omløpsmidler,Egenkapital,Langsiktig gjeld,Kortsiktig gjeld"</formula1>
+      <formula1>$Z$26:$Z$30</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C19" type="list">
-      <formula1>"Anleggsmidler,Omløpsmidler,Egenkapital,Langsiktig gjeld,Kortsiktig gjeld"</formula1>
+      <formula1>$Z$31:$Z$35</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C20" type="list">
-      <formula1>"Anleggsmidler,Omløpsmidler,Egenkapital,Langsiktig gjeld,Kortsiktig gjeld"</formula1>
+      <formula1>$Z$36:$Z$40</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C21" type="list">
-      <formula1>"Anleggsmidler,Omløpsmidler,Egenkapital,Langsiktig gjeld,Kortsiktig gjeld"</formula1>
+      <formula1>$Z$41:$Z$45</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C22" type="list">
-      <formula1>"Anleggsmidler,Omløpsmidler,Egenkapital,Langsiktig gjeld,Kortsiktig gjeld"</formula1>
+      <formula1>$Z$46:$Z$50</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C23" type="list">
-      <formula1>"Anleggsmidler,Omløpsmidler,Egenkapital,Langsiktig gjeld,Kortsiktig gjeld"</formula1>
+      <formula1>$Z$51:$Z$55</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C37" type="list">
@@ -3542,7 +3923,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G44"/>
+  <dimension ref="B1:Z44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -3550,381 +3931,393 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>146</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>141</v>
+      <c r="B11" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>300000</v>
       </c>
-      <c r="D12" s="13"/>
+      <c r="D12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="13" t="n">
         <v>80000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="C14" s="12" t="n">
+      <c r="B14" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="13" t="n">
         <v>500000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="B15" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="13" t="n">
         <v>500000</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="13" t="n">
         <v>563257</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="B16" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>800000</v>
       </c>
-      <c r="D16" s="13"/>
+      <c r="D16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="12" t="n">
+      <c r="B17" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="13" t="n">
         <v>300000</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="13" t="n">
         <v>300000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="C18" s="12" t="n">
+      <c r="B18" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="13"/>
+      <c r="D18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="C19" s="12" t="n">
+      <c r="B19" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="13" t="n">
         <v>500000</v>
       </c>
-      <c r="D19" s="13"/>
+      <c r="D19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="C20" s="12" t="n">
+      <c r="B20" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="C20" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="13" t="n">
         <v>381600</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C21" s="12" t="n">
+      <c r="B21" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C21" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="13" t="n">
         <v>218400</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C22" s="12" t="n">
+      <c r="B22" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" s="13" t="n">
         <v>800000</v>
       </c>
-      <c r="D22" s="13"/>
+      <c r="D22" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+      <c r="B24" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="B25" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="14" t="s">
-        <v>51</v>
+      <c r="B27" s="15" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="C28" s="15" t="str">
+        <v>168</v>
+      </c>
+      <c r="C28" s="16" t="str">
         <f aca="false">IF(D12="","Skriv svaret i cellen D12.",IF(D12=(300000-60000),"Riktig.",IF(D12=(300000),"Utstyret står med kjøpesummen. Årets avskrivning på 60 000 skal trekkes fra; det er den som var kostnad i 1C.",IF(D12=(60000),"Det er avskrivningen. Bokført verdi er det som er igjen: 300 000 minus 60 000.","Ikke riktig ennå. Bokført verdi er kjøpesum minus avskrivningene til nå."))))</f>
         <v>Skriv svaret i cellen D12.</v>
       </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="C29" s="15" t="str">
+        <v>169</v>
+      </c>
+      <c r="C29" s="16" t="str">
         <f aca="false">IF(D18="","Skriv svaret i cellen D18.",IF(D18=(83257),"Riktig.",IF(D18=(106740),"Det er resultat før skatt. Det er årsresultatet etter skatt, 83 257, som legges til egenkapitalen.",IF(D18=(144240),"Det er driftsresultatet. Renter og skatt skal trekkes fra først; årsresultatet er 83 257.",IF(D18=(383257),"Du har lagt til aksjekapitalen. Den står på sin egen linje; annen egenkapital er bare det opptjente overskuddet.","Ikke riktig ennå. Annen egenkapital er egenkapitalen ved starten pluss årsresultatet minus utbytte.")))))</f>
         <v>Skriv svaret i cellen D18.</v>
       </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
     </row>
     <row r="30" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="C30" s="15" t="str">
+        <v>170</v>
+      </c>
+      <c r="C30" s="16" t="str">
         <f aca="false">IF(D19="","Skriv svaret i cellen D19.",IF(D19=(500000-100000),"Riktig.",IF(D19=(500000),"Lånet står som ved starten. Avdraget på 100 000 har redusert det.",IF(D19=(500000-37500),"Du har trukket fra rentene. Rentene er en kostnad i resultatregnskapet; det er avdraget som reduserer lånet.","Ikke riktig ennå. Lånet ved slutten er lånet ved starten minus avdraget."))))</f>
         <v>Skriv svaret i cellen D19.</v>
       </c>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
     </row>
     <row r="31" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="C31" s="15" t="str">
+        <v>171</v>
+      </c>
+      <c r="C31" s="16" t="str">
         <f aca="false">IF(D16="","Skriv svaret i cellen D16.",IF(D16=(240000+80000+500000+563257),"Riktig.",IF(D16=(300000+80000+500000+563257),"Utstyret står med kjøpesummen 300 000. Trekk fra avskrivningen først.","Ikke riktig ennå. Summer utstyr, varelager, kundefordringer og bankinnskudd.")))</f>
         <v>Skriv svaret i cellen D16.</v>
       </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
     </row>
     <row r="32" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="C32" s="15" t="str">
+        <v>172</v>
+      </c>
+      <c r="C32" s="16" t="str">
         <f aca="false">IF(D22="","Skriv svaret i cellen D22.",IF(D22=(300000+83257+400000+381600+218400),"Riktig.",IF(D22=(300000+83257+500000+381600+218400),"Banklånet står med 500 000. Avdraget på 100 000 skal trekkes fra.","Ikke riktig ennå. Summer aksjekapital, annen egenkapital, banklån og den kortsiktige gjelden. Summen skal bli lik sum eiendeler, 1 383 257.")))</f>
         <v>Skriv svaret i cellen D22.</v>
       </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="C34" s="17"/>
-      <c r="G34" s="18" t="str">
+      <c r="B34" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="G34" s="19" t="str">
         <f aca="false">IF(C34="","Velg i nedtrekksmenyen.",IF(C34="I balansen: bankinnskudd ned og banklån ned","Riktig. Et avdrag flytter penger fra bankinnskudd til nedbetalt gjeld inne i balansen, like mye på hver post. Det er ikke en kostnad, og det står ikke i resultatregnskapet. Bare rentene gjør det.","Ikke riktig. Et avdrag flytter penger fra bankinnskudd til nedbetalt gjeld inne i balansen, like mye på hver post. Det er ikke en kostnad, og det står ikke i resultatregnskapet. Bare rentene gjør det."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
+      <c r="B36" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="20" t="str">
+      <c r="B40" s="21" t="str">
         <f aca="false">IF(LEN(B37)&lt;40,"",IF(AND(ISNUMBER(SEARCH("gjeld",B37)),ISNUMBER(SEARCH("bank",B37))),"Bra: du holder bankinnskuddet opp mot den kortsiktige gjelden. 563 257 i banken dekker ikke 600 000 som forfaller i år, og utbytte på 80 000 gjør det verre. Egenkapitalen er ikke penger på konto.",IF(OR(ISNUMBER(SEARCH("gjeld",B37)),ISNUMBER(SEARCH("bank",B37))),"Du er på sporet. Hold bankinnskuddet 563 257 opp mot den kortsiktige gjelden 600 000, og si hva et utbytte på 80 000 gjør med den.","Tips: egenkapital er ikke penger. På konto står 563 257, og 600 000 forfaller i år. Tar eieren ut 80 000, synker kontoen til 483 257. Aksjeloven krever forsvarlig egenkapital og likviditet etter utbyttet. Rådet er å la overskuddet stå.")))</f>
         <v/>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" s="17"/>
+      <c r="B41" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="18"/>
     </row>
     <row r="42" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="21" t="str">
+      <c r="B42" s="22" t="str">
         <f aca="false">IF(C41="JA","Hint: Utstyr: 300 000 − 60 000 = 240 000. Annen egenkapital: 0 + 83 257 − 0 = 83 257. Banklån: 500 000 − 100 000 = 400 000. Eiendeler: 240 000 + 80 000 + 500 000 + 563 257 = 1 383 257. Egenkapital og gjeld: 300 000 + 83 257 + 400 000 + 381 600 + 218 400 = 1 383 257.","")</f>
         <v/>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
+      <c r="B44" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -3999,7 +4392,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C34" type="list">
-      <formula1>"I resultatregnskapet,som kostnad,I balansen: bankinnskudd ned og banklån ned,Begge steder"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C41" type="list">
@@ -4022,7 +4415,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G39"/>
+  <dimension ref="B1:Z39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -4030,342 +4423,452 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>175</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="Z11" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="Z12" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
+      <c r="D13" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z13" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>10482650</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>9882650</v>
+      </c>
+      <c r="Z14" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>10802650</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>10182650</v>
+      </c>
+      <c r="Z15" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>10182650</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>9272000</v>
+      </c>
+      <c r="Z16" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z17" s="0" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="Z18" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="Z19" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z20" s="0" t="s">
         <v>162</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-    </row>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>10482650</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>9882650</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>10802650</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>10182650</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>10182650</v>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>9272000</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G21" s="18" t="str">
+      <c r="B21" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G21" s="19" t="str">
         <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(10482650-9882650),"Riktig.",IF(ABS(C21-(10482650+9882650))&lt;=0,"Du har lagt sammen. Differansen er det største tallet minus det minste.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z21" s="6" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="C22" s="17"/>
-      <c r="G22" s="18" t="str">
+      <c r="B22" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="G22" s="19" t="str">
         <f aca="false">IF(C22="","Velg i nedtrekksmenyen.",IF(C22="Står på feil side","Riktig. 600 000 er det dobbelte av kassekreditten på 300 000. For mye på den ene siden og for lite på den andre: derfor dobbelt.","Ikke riktig. 600 000 er det dobbelte av kassekreditten på 300 000. For mye på den ene siden og for lite på den andre: derfor dobbelt."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z22" s="6" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="C23" s="17"/>
-      <c r="G23" s="18" t="str">
+      <c r="B23" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="G23" s="19" t="str">
         <f aca="false">IF(C23="","Velg i nedtrekksmenyen.",IF(C23="Kassekreditten","Riktig. Kassekreditten er lagt til bankinnskuddet (1 282 650 i stedet for 982 650) og mangler under kortsiktig gjeld. Den er lånte penger.","Ikke riktig. Kassekreditten er lagt til bankinnskuddet (1 282 650 i stedet for 982 650) og mangler under kortsiktig gjeld. Den er lånte penger."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z23" s="6" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="18" t="str">
+      <c r="B24" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" s="19" t="str">
         <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(C24=(10802650-10182650),"Riktig.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z24" s="6" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="G25" s="18" t="str">
+      <c r="B25" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="G25" s="19" t="str">
         <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="Anleggsmidlene er ikke satt ned","Riktig. 620 000 er årets avskrivning. Den er trukket i resultatregnskapet, men bilene og verktøyet står med fjorårets verdi.","Ikke riktig. 620 000 er årets avskrivning. Den er trukket i resultatregnskapet, men bilene og verktøyet står med fjorårets verdi."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z25" s="6" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="G26" s="18" t="str">
+      <c r="B26" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="G26" s="19" t="str">
         <f aca="false">IF(C26="","Velg i nedtrekksmenyen.",IF(C26="Anleggsmidlene","Riktig. Anleggsmidlene står med 4 220 000 i stedet for 3 600 000. Sett dem ned med avskrivningen.","Ikke riktig. Anleggsmidlene står med 4 220 000 i stedet for 3 600 000. Sett dem ned med avskrivningen."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z26" s="6" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27" s="18" t="str">
+      <c r="B27" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="19" t="str">
         <f aca="false">IF(C27="","Skriv svaret i den gule cellen.",IF(C27=(10182650-9272000),"Riktig.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z27" s="6" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="C28" s="17"/>
-      <c r="G28" s="18" t="str">
+      <c r="B28" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="G28" s="19" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Egenkapitalen er ikke oppdatert","Riktig. 910 650 er årsresultatet. Årets overskudd er ikke lagt til annen egenkapital.","Ikke riktig. 910 650 er årsresultatet. Årets overskudd er ikke lagt til annen egenkapital."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z28" s="6" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="C29" s="17"/>
-      <c r="G29" s="18" t="str">
+      <c r="B29" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="G29" s="19" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Annen egenkapital","Riktig. Annen egenkapital står med fjorårets 1 682 000. Riktig er 1 682 000 + 910 650 = 2 592 650.","Ikke riktig. Annen egenkapital står med fjorårets 1 682 000. Riktig er 1 682 000 + 910 650 = 2 592 650."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z29" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z30" s="0" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="B31" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="Z31" s="6" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="Z32" s="6" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="Z33" s="6" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="20" t="str">
+      <c r="B35" s="21" t="str">
         <f aca="false">IF(LEN(B32)&lt;40,"",IF(AND(ISNUMBER(SEARCH("bank",B32)),ISNUMBER(SEARCH("kundefordring",B32))),"Bra: du skiller egenkapitalen fra pengene på konto og peker på kundefordringene. Egenkapitalen sier hvem som har betalt for eiendelene, ikke hvor pengene er.",IF(OR(ISNUMBER(SEARCH("bank",B32)),ISNUMBER(SEARCH("kundefordring",B32))),"Du er på sporet. Si hvor pengene faktisk står: 982 650 i banken, 4 200 000 hos kundene og 1 400 000 på lageret.","Tips: egenkapitalen på 2 892 650 er eiendeler minus gjeld, ikke penger på konto. I banken står 982 650. Kundene skylder 4 200 000, og lageret binder 1 400 000. Pengene er ikke borte, de er underveis.")))</f>
         <v/>
       </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="17"/>
+      <c r="B36" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="18"/>
     </row>
     <row r="37" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="21" t="str">
+      <c r="B37" s="22" t="str">
         <f aca="false">IF(C36="JA","Hint: A: 10 482 650 − 9 882 650 = 600 000 = 2 × 300 000, kassekreditten på feil side. B: 10 802 650 − 10 182 650 = 620 000 = avskrivningen, anleggsmidlene ikke satt ned. C: 10 182 650 − 9 272 000 = 910 650 = årsresultatet, annen egenkapital ikke oppdatert.","")</f>
         <v/>
       </c>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
+      <c r="B39" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -4461,27 +4964,27 @@
   </conditionalFormatting>
   <dataValidations count="7">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C22" type="list">
-      <formula1>"Glemt eller telt to ganger,Står på feil side,Egenkapitalen er ikke oppdatert,Anleggsmidlene er ikke satt ned,Regnefeil"</formula1>
+      <formula1>$Z$1:$Z$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C23" type="list">
-      <formula1>"Kassekreditten,Bankinnskuddet,Anleggsmidlene,Annen egenkapital,Kundefordringene,Avskrivningene"</formula1>
+      <formula1>$Z$6:$Z$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Glemt eller telt to ganger,Står på feil side,Egenkapitalen er ikke oppdatert,Anleggsmidlene er ikke satt ned,Regnefeil"</formula1>
+      <formula1>$Z$12:$Z$16</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C26" type="list">
-      <formula1>"Kassekreditten,Bankinnskuddet,Anleggsmidlene,Annen egenkapital,Kundefordringene,Avskrivningene"</formula1>
+      <formula1>$Z$17:$Z$22</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Glemt eller telt to ganger,Står på feil side,Egenkapitalen er ikke oppdatert,Anleggsmidlene er ikke satt ned,Regnefeil"</formula1>
+      <formula1>$Z$23:$Z$27</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Kassekreditten,Bankinnskuddet,Anleggsmidlene,Annen egenkapital,Kundefordringene,Avskrivningene"</formula1>
+      <formula1>$Z$28:$Z$33</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C36" type="list">
@@ -4514,378 +5017,378 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="24" t="s">
-        <v>182</v>
+      <c r="B2" s="25" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>186</v>
+      <c r="B5" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="27" t="n">
+      <c r="B6" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="28" t="n">
         <v>8390000</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>188</v>
+      <c r="D6" s="27" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="C7" s="27" t="n">
+      <c r="B7" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="28" t="n">
         <v>14010000</v>
       </c>
-      <c r="D7" s="26" t="s">
-        <v>190</v>
+      <c r="D7" s="27" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="C8" s="27" t="n">
+      <c r="B8" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="28" t="n">
         <v>1344000</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>192</v>
+      <c r="D8" s="27" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="C9" s="27" t="n">
+      <c r="B9" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="28" t="n">
         <v>1167500</v>
       </c>
-      <c r="D9" s="26" t="s">
-        <v>194</v>
+      <c r="D9" s="27" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="C10" s="27" t="n">
+      <c r="B10" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" s="28" t="n">
         <v>910650</v>
       </c>
-      <c r="D10" s="26" t="s">
-        <v>196</v>
+      <c r="D10" s="27" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="26" t="s">
-        <v>198</v>
+      <c r="B11" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="27" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="26" t="s">
-        <v>200</v>
+      <c r="B12" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="27" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="26" t="s">
-        <v>202</v>
+      <c r="B13" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="27" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="C14" s="27" t="n">
+      <c r="B14" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="C14" s="28" t="n">
         <v>138500</v>
       </c>
-      <c r="D14" s="26" t="s">
-        <v>204</v>
+      <c r="D14" s="27" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="C15" s="27" t="n">
+      <c r="B15" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="28" t="n">
         <v>533500</v>
       </c>
-      <c r="D15" s="26" t="s">
-        <v>206</v>
+      <c r="D15" s="27" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="C16" s="27" t="n">
+      <c r="B16" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="C16" s="28" t="n">
         <v>270000</v>
       </c>
-      <c r="D16" s="26" t="s">
-        <v>208</v>
+      <c r="D16" s="27" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="26" t="s">
-        <v>210</v>
+      <c r="B17" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="27" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="C18" s="27" t="n">
+      <c r="B18" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C18" s="28" t="n">
         <v>3395000</v>
       </c>
-      <c r="D18" s="26" t="s">
-        <v>212</v>
+      <c r="D18" s="27" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="C19" s="27" t="n">
+      <c r="B19" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="C19" s="28" t="n">
         <v>144240</v>
       </c>
-      <c r="D19" s="26" t="s">
-        <v>214</v>
+      <c r="D19" s="27" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="C20" s="27" t="n">
+      <c r="B20" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="C20" s="28" t="n">
         <v>106740</v>
       </c>
-      <c r="D20" s="26" t="s">
-        <v>216</v>
+      <c r="D20" s="27" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C21" s="27" t="n">
+      <c r="B21" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="C21" s="28" t="n">
         <v>83257</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>218</v>
+      <c r="D21" s="27" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="26" t="s">
-        <v>220</v>
+      <c r="B22" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="C22" s="28"/>
+      <c r="D22" s="27" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="26" t="s">
-        <v>222</v>
+      <c r="B23" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="27" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="26" t="s">
-        <v>224</v>
+      <c r="B24" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="27" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="C25" s="27" t="n">
+      <c r="B25" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="C25" s="28" t="n">
         <v>6582650</v>
       </c>
-      <c r="D25" s="26" t="s">
-        <v>226</v>
+      <c r="D25" s="27" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="C26" s="27" t="n">
+      <c r="B26" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C26" s="28" t="n">
         <v>4490000</v>
       </c>
-      <c r="D26" s="26" t="s">
-        <v>228</v>
+      <c r="D26" s="27" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="C27" s="27" t="n">
+      <c r="B27" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="C27" s="28" t="n">
         <v>10182650</v>
       </c>
-      <c r="D27" s="26" t="s">
-        <v>230</v>
+      <c r="D27" s="27" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="C28" s="27" t="n">
+      <c r="B28" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="C28" s="28" t="n">
         <v>28.4</v>
       </c>
-      <c r="D28" s="26" t="s">
-        <v>232</v>
+      <c r="D28" s="27" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="C29" s="27"/>
-      <c r="D29" s="26" t="s">
-        <v>234</v>
+      <c r="B29" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="C29" s="28"/>
+      <c r="D29" s="27" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="C30" s="27" t="n">
+      <c r="B30" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="C30" s="28" t="n">
         <v>240000</v>
       </c>
-      <c r="D30" s="26" t="s">
-        <v>236</v>
+      <c r="D30" s="27" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="C31" s="27" t="n">
+      <c r="B31" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C31" s="28" t="n">
         <v>83257</v>
       </c>
-      <c r="D31" s="26" t="s">
-        <v>238</v>
+      <c r="D31" s="27" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="C32" s="27" t="n">
+      <c r="B32" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C32" s="28" t="n">
         <v>400000</v>
       </c>
-      <c r="D32" s="26" t="s">
-        <v>240</v>
+      <c r="D32" s="27" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="C33" s="27" t="n">
+      <c r="B33" s="27" t="s">
+        <v>266</v>
+      </c>
+      <c r="C33" s="28" t="n">
         <v>1383257</v>
       </c>
-      <c r="D33" s="26" t="s">
-        <v>242</v>
+      <c r="D33" s="27" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="C34" s="27"/>
-      <c r="D34" s="26" t="s">
-        <v>244</v>
+      <c r="B34" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="27" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="C35" s="27"/>
-      <c r="D35" s="26" t="s">
-        <v>246</v>
+      <c r="B35" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C35" s="28"/>
+      <c r="D35" s="27" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="C36" s="27" t="n">
+      <c r="B36" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C36" s="28" t="n">
         <v>600000</v>
       </c>
-      <c r="D36" s="26" t="s">
-        <v>248</v>
+      <c r="D36" s="27" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="C37" s="27" t="n">
+      <c r="B37" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="C37" s="28" t="n">
         <v>620000</v>
       </c>
-      <c r="D37" s="26" t="s">
-        <v>250</v>
+      <c r="D37" s="27" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="C38" s="27" t="n">
+      <c r="B38" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="C38" s="28" t="n">
         <v>910650</v>
       </c>
-      <c r="D38" s="26" t="s">
-        <v>252</v>
+      <c r="D38" s="27" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="C39" s="27"/>
-      <c r="D39" s="26" t="s">
-        <v>254</v>
+      <c r="B39" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="C39" s="28"/>
+      <c r="D39" s="27" t="s">
+        <v>279</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ok03/OK03_Bedriftens_regnskap_Oppgaver_v6.xlsx
+++ b/pensum/ok03/OK03_Bedriftens_regnskap_Oppgaver_v6.xlsx
@@ -238,7 +238,7 @@
     <t xml:space="preserve">Varekostnad</t>
   </si>
   <si>
-    <t xml:space="preserve">Tom (driftsleder) har handlet i januar 2027: en servicebil, et varmekamera, en boremaskin og kabel til en jobb. Han spør hvor mye av dette som er kostnad i år, og hvorfor regnskapsføreren sier at bilen nesten ikke koster noe i 2027.</t>
+    <t xml:space="preserve">Tom (driftsleder) har handlet i januar 2027: en servicebil, betalt med et nytt banklån, og fra kontoen en kabelsøker, en boremaskin og kabel til en jobb. Han spør hvor mye av dette som er kostnad i år, og hvorfor regnskapsføreren sier at bilen nesten ikke koster noe i 2027.</t>
   </si>
   <si>
     <t xml:space="preserve">Aktivere: føre kjøpet i balansen som eiendel og fordele kostnaden over brukstiden gjennom avskrivning. Lineær avskrivning: samme beløp hvert år, kjøpesum delt på brukstid. Bokført verdi: kjøpesum minus avskrivningene til nå. Varekostnad: materiell som er brukt opp hos kunden.</t>
@@ -259,7 +259,7 @@
     <t xml:space="preserve">Servicebil</t>
   </si>
   <si>
-    <t xml:space="preserve">Varmekamera</t>
+    <t xml:space="preserve">Kabelsøker</t>
   </si>
   <si>
     <t xml:space="preserve">Boremaskin</t>
@@ -270,7 +270,7 @@
   <si>
     <t xml:space="preserve">1. Velg for hvert kjøp hvordan det behandles i regnskapet (nedtrekksmenyen).
 2. Regn hvor mye av de fire kjøpene som er kostnad i 2027. For det som aktiveres, er det bare avskrivningen: beløp delt på brukstid.
-3. Regn hvor mye som gikk ut av bankkontoen i januar.
+3. Regn hvor mye som ble betalt ut for de fire kjøpene i januar (bilen betales med lånepengene, resten fra kontoen).
 4. Regn hva servicebilen står med i balansen 31.12.2028, etter to års lineær avskrivning.</t>
   </si>
   <si>
@@ -280,7 +280,7 @@
     <t xml:space="preserve">Servicebil 450 000 kr, fem år</t>
   </si>
   <si>
-    <t xml:space="preserve">Varmekamera 42 000 kr, seks år</t>
+    <t xml:space="preserve">Kabelsøker 42 000 kr, seks år</t>
   </si>
   <si>
     <t xml:space="preserve">Boremaskin 3 500 kr, tre år</t>
@@ -295,7 +295,7 @@
     <t xml:space="preserve">kr</t>
   </si>
   <si>
-    <t xml:space="preserve">b) Ut av bankkontoen i januar 2027 (alt betales kontant)</t>
+    <t xml:space="preserve">b) Betalt ut for de fire kjøpene i januar 2027 (bilen med lånepengene, resten fra kontoen)</t>
   </si>
   <si>
     <t xml:space="preserve">c) Bokført verdi på servicebilen 31.12.2028, etter to års avskrivning</t>
@@ -585,7 +585,7 @@
     <t xml:space="preserve">Anleggsmidlene er ikke satt ned</t>
   </si>
   <si>
-    <t xml:space="preserve">Tre studenter har satt opp Nordlys' balanse per 31.12.2026, og ingen av dem går opp. Samtidig sier Tom (driftsleder): «Vi har 2,9 millioner i egenkapital. Vi har råd til lastebilen.» Finn feilene, og forklar Tom hva egenkapitalen er.</t>
+    <t xml:space="preserve">Tre studenter har satt opp Nordlys' balanse per 31.12.2026, og ingen av dem går opp. Samtidig sier Tom (driftsleder): «Vi har 2,9 millioner i egenkapital. Vi har råd til servicebilene.» Finn feilene, og forklar Tom hva egenkapitalen er.</t>
   </si>
   <si>
     <t xml:space="preserve">Regnefeil</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">   Student C: hvilken post?</t>
   </si>
   <si>
-    <t xml:space="preserve">d) Tom sier: «Vi har 2,9 millioner i egenkapital. Vi har råd til lastebilen.» Forklar Tom hva egenkapitalen er, og hvor pengene faktisk står. Bruk tallene fra balansen. To–tre setninger.</t>
+    <t xml:space="preserve">d) Tom sier: «Vi har 2,9 millioner i egenkapital. Vi har råd til to servicebiler til.» Forklar Tom hva egenkapitalen er, og hvor pengene faktisk står. Bruk tallene fra balansen. To–tre setninger.</t>
   </si>
   <si>
     <t xml:space="preserve">Fasit, kapittel 3</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">1B Sorteringen</t>
   </si>
   <si>
-    <t xml:space="preserve">Aktiveres: servicebil og varmekamera. Kostnad med én gang: boremaskin. Varekostnad: kabel og sikringsmateriell</t>
+    <t xml:space="preserve">Aktiveres: servicebil og kabelsøker. Kostnad med én gang: boremaskin. Varekostnad: kabel og sikringsmateriell</t>
   </si>
   <si>
     <t xml:space="preserve">1B a) Kostnad i 2027</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">90 000 + 7 000 + 3 500 + 38 000 = 138 500 kr</t>
   </si>
   <si>
-    <t xml:space="preserve">1B b) Ut av banken</t>
+    <t xml:space="preserve">1B b) Betalt ut</t>
   </si>
   <si>
     <t xml:space="preserve">450 000 + 42 000 + 3 500 + 38 000 = 533 500 kr</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">1B d) Forskjellen</t>
   </si>
   <si>
-    <t xml:space="preserve">395 000 kr står i balansen som bil og kamera og blir kostnad gjennom avskrivningene, 97 000 kr i året</t>
+    <t xml:space="preserve">395 000 kr står i balansen som bil og kabelsøker og blir kostnad gjennom avskrivningene, 97 000 kr i året</t>
   </si>
   <si>
     <t xml:space="preserve">1C a) Bruttofortjeneste</t>
@@ -2172,7 +2172,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
         <v>68</v>
       </c>
@@ -2313,7 +2313,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="s">
         <v>78</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>85</v>
       </c>
       <c r="G26" s="19" t="str">
-        <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(C26=(450000/5+42000/6+3500+38000),"Riktig.",IF(ABS(C26-(450000+42000+3500+38000))&lt;=0,"Du har tatt hele beløpene. Bilen og kameraet aktiveres; bare avskrivningen er kostnad i år.",IF(ABS(C26-(450000/5+42000/6))&lt;=0,"Du har tatt bare avskrivningene. Boremaskinen og kabelen er kostnad i år, med hele beløpet.",IF(ABS(C26-(450000/5+42000/6+3500))&lt;=0,"Du har glemt kabelen, 38 000. Den er varekostnad i år.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
+        <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(C26=(450000/5+42000/6+3500+38000),"Riktig.",IF(ABS(C26-(450000+42000+3500+38000))&lt;=0,"Du har tatt hele beløpene. Bilen og kabelsøkeren aktiveres; bare avskrivningen er kostnad i år.",IF(ABS(C26-(450000/5+42000/6))&lt;=0,"Du har tatt bare avskrivningene. Boremaskinen og kabelen er kostnad i år, med hele beløpet.",IF(ABS(C26-(450000/5+42000/6+3500))&lt;=0,"Du har glemt kabelen, 38 000. Den er varekostnad i år.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="21" t="str">
-        <f aca="false">IF(LEN(B31)&lt;40,"",IF(AND(ISNUMBER(SEARCH("balanse",B31)),ISNUMBER(SEARCH("avskriv",B31))),"Bra: du sier at forskjellen står i balansen som eiendel, og at den blir kostnad gjennom avskrivningene de neste årene.",IF(OR(ISNUMBER(SEARCH("balanse",B31)),ISNUMBER(SEARCH("avskriv",B31))),"Du er på sporet. Si både hvor pengene står nå (i balansen, som bil og kamera) og hva som skjer med dem videre (avskrivningene).","Tips: 533 500 − 138 500 = 395 000 kr står i balansen som servicebil og varmekamera. De blir kostnad litt hvert år gjennom avskrivningene, 97 000 kr i året.")))</f>
+        <f aca="false">IF(LEN(B31)&lt;40,"",IF(AND(ISNUMBER(SEARCH("balanse",B31)),ISNUMBER(SEARCH("avskriv",B31))),"Bra: du sier at forskjellen står i balansen som eiendel, og at den blir kostnad gjennom avskrivningene de neste årene.",IF(OR(ISNUMBER(SEARCH("balanse",B31)),ISNUMBER(SEARCH("avskriv",B31))),"Du er på sporet. Si både hvor pengene står nå (i balansen, som bil og kabelsøker) og hva som skjer med dem videre (avskrivningene).","Tips: 533 500 − 138 500 = 395 000 kr står i balansen som servicebil og kabelsøker. De blir kostnad litt hvert år gjennom avskrivningene, 97 000 kr i året.")))</f>
         <v/>
       </c>
       <c r="C34" s="21"/>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="22" t="str">
-        <f aca="false">IF(C35="JA","Hint: Kostnad i år: 450 000 / 5 = 90 000, pluss 42 000 / 6 = 7 000, pluss 3 500, pluss 38 000 = 138 500. Ut av banken: 450 000 + 42 000 + 3 500 + 38 000 = 533 500. Bilen etter to år: 450 000 − 2 × 90 000 = 270 000.","")</f>
+        <f aca="false">IF(C35="JA","Hint: Kostnad i år: 450 000 / 5 = 90 000, pluss 42 000 / 6 = 7 000, pluss 3 500, pluss 38 000 = 138 500. Betalt ut: 450 000 + 42 000 + 3 500 + 38 000 = 533 500. Bilen etter to år: 450 000 − 2 × 90 000 = 270 000.","")</f>
         <v/>
       </c>
       <c r="C36" s="22"/>

--- a/pensum/ok03/OK03_Bedriftens_regnskap_Oppgaver_v6.xlsx
+++ b/pensum/ok03/OK03_Bedriftens_regnskap_Oppgaver_v6.xlsx
@@ -1063,7 +1063,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1178,6 +1178,10 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1465,7 +1469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1490,42 +1494,42 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
@@ -1743,7 +1747,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="9" t="s">
         <v>39</v>
       </c>
@@ -1857,7 +1861,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
     </row>
-    <row r="39" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="90" customHeight="true" r="39" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="9" t="s">
         <v>53</v>
       </c>
@@ -2292,8 +2296,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="29" r="B15" t="s">
         <v>77</v>
       </c>
       <c r="C15" s="13" t="n">
@@ -2323,7 +2327,7 @@
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="8" t="s">
         <v>79</v>
       </c>
@@ -2809,7 +2813,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="75.75" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="9" t="s">
         <v>103</v>
       </c>
@@ -2871,7 +2875,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="29" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="8" t="s">
         <v>108</v>
       </c>
@@ -3287,7 +3291,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="8" t="s">
         <v>126</v>
       </c>
@@ -4157,7 +4161,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="75.75" customHeight="true" r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="9" t="s">
         <v>167</v>
       </c>
@@ -4640,7 +4644,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
         <v>196</v>
       </c>
